--- a/salidas/empresas/EBAY.xlsx
+++ b/salidas/empresas/EBAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.99677658081055</v>
+        <v>15.99677562713623</v>
       </c>
       <c r="C2" t="n">
         <v>18.13973045349121</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.86847019195557</v>
+        <v>14.8684663772583</v>
       </c>
       <c r="C3" t="n">
         <v>16.86026954650879</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.47504043579102</v>
+        <v>14.47504234313965</v>
       </c>
       <c r="C4" t="n">
         <v>16.41414070129395</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.77144241333008</v>
+        <v>12.77144145965576</v>
       </c>
       <c r="C5" t="n">
         <v>14.48232269287109</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.17759609222412</v>
+        <v>12.1775951385498</v>
       </c>
       <c r="C6" t="n">
         <v>13.80892276763916</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.32553195953369</v>
+        <v>10.32553005218506</v>
       </c>
       <c r="C9" t="n">
         <v>11.70875358581543</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>10.52595520019531</v>
+        <v>10.525954246521</v>
       </c>
       <c r="C10" t="n">
         <v>11.93602657318115</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.92520713806152</v>
+        <v>11.92521095275879</v>
       </c>
       <c r="C11" t="n">
         <v>13.52272701263428</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.00315189361572</v>
+        <v>12.00315284729004</v>
       </c>
       <c r="C12" t="n">
         <v>13.61111068725586</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.16062927246094</v>
+        <v>11.16062641143799</v>
       </c>
       <c r="C13" t="n">
         <v>12.65572357177734</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.02170848846436</v>
+        <v>12.02171039581299</v>
       </c>
       <c r="C14" t="n">
         <v>13.632155418396</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.8992280960083</v>
+        <v>11.89922618865967</v>
       </c>
       <c r="C15" t="n">
         <v>13.49326610565186</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>12.59699630737305</v>
+        <v>12.59699821472168</v>
       </c>
       <c r="C17" t="n">
         <v>14.28451156616211</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>12.08480548858643</v>
+        <v>12.08480358123779</v>
       </c>
       <c r="C18" t="n">
         <v>13.70370388031006</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>11.94376468658447</v>
+        <v>11.94376373291016</v>
       </c>
       <c r="C19" t="n">
         <v>13.5437707901001</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.65638542175293</v>
+        <v>12.6563835144043</v>
       </c>
       <c r="C21" t="n">
         <v>14.35185241699219</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>14.48246765136719</v>
+        <v>14.48246574401855</v>
       </c>
       <c r="C22" t="n">
         <v>16.42255973815918</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>13.39869117736816</v>
+        <v>13.39869403839111</v>
       </c>
       <c r="C23" t="n">
         <v>15.19360256195068</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>11.07526397705078</v>
+        <v>11.0752649307251</v>
       </c>
       <c r="C28" t="n">
         <v>12.55892276763916</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.13836097717285</v>
+        <v>11.13835716247559</v>
       </c>
       <c r="C30" t="n">
         <v>12.63047122955322</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.14366626739502</v>
+        <v>10.14366149902344</v>
       </c>
       <c r="C31" t="n">
         <v>11.50252532958984</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>9.341971397399902</v>
+        <v>9.34196949005127</v>
       </c>
       <c r="C32" t="n">
         <v>10.59343433380127</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>9.252893447875977</v>
+        <v>9.252895355224609</v>
       </c>
       <c r="C33" t="n">
         <v>10.49242401123047</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>8.306447982788086</v>
+        <v>8.306448936462402</v>
       </c>
       <c r="C34" t="n">
         <v>9.419192314147949</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.667535305023193</v>
+        <v>5.667535781860352</v>
       </c>
       <c r="C35" t="n">
         <v>6.426767826080322</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.18132209777832</v>
+        <v>5.181323051452637</v>
       </c>
       <c r="C37" t="n">
         <v>5.875421047210693</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.461282253265381</v>
+        <v>4.461283206939697</v>
       </c>
       <c r="C38" t="n">
         <v>5.05892276763916</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>4.034455299377441</v>
+        <v>4.034453392028809</v>
       </c>
       <c r="C39" t="n">
         <v>4.574915885925293</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>4.661704540252686</v>
+        <v>4.66170597076416</v>
       </c>
       <c r="C40" t="n">
         <v>5.286194801330566</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>6.539750099182129</v>
+        <v>6.539749145507812</v>
       </c>
       <c r="C42" t="n">
         <v>7.415824890136719</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>6.357885360717773</v>
+        <v>6.357882976531982</v>
       </c>
       <c r="C43" t="n">
         <v>7.209596157073975</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.887040138244629</v>
+        <v>7.88704252243042</v>
       </c>
       <c r="C44" t="n">
         <v>8.943602561950684</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>8.217370986938477</v>
+        <v>8.217369079589844</v>
       </c>
       <c r="C45" t="n">
         <v>9.318181991577148</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>8.759256362915039</v>
+        <v>8.759257316589355</v>
       </c>
       <c r="C46" t="n">
         <v>9.932660102844238</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>8.265623092651367</v>
+        <v>8.265619277954102</v>
       </c>
       <c r="C47" t="n">
         <v>9.372896194458008</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>9.082160949707031</v>
+        <v>9.082161903381348</v>
       </c>
       <c r="C48" t="n">
         <v>10.2988224029541</v>
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.543985366821289</v>
+        <v>8.543986320495605</v>
       </c>
       <c r="C50" t="n">
         <v>9.688551902770996</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.543985366821289</v>
+        <v>8.543986320495605</v>
       </c>
       <c r="C51" t="n">
         <v>9.688551902770996</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.01004981994629</v>
+        <v>10.01004791259766</v>
       </c>
       <c r="C52" t="n">
         <v>11.3510103225708</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>8.826064109802246</v>
+        <v>8.826065063476562</v>
       </c>
       <c r="C53" t="n">
         <v>10.00841808319092</v>
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.27834939956665</v>
+        <v>7.278347492218018</v>
       </c>
       <c r="C55" t="n">
         <v>8.25336742401123</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.76085090637207</v>
+        <v>7.760849952697754</v>
       </c>
       <c r="C56" t="n">
         <v>8.800504684448242</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.621930122375488</v>
+        <v>8.621928215026855</v>
       </c>
       <c r="C57" t="n">
         <v>9.776935577392578</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.056181907653809</v>
+        <v>9.056180953979492</v>
       </c>
       <c r="C58" t="n">
         <v>10.26935958862305</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>11.08268642425537</v>
+        <v>11.08268547058105</v>
       </c>
       <c r="C59" t="n">
         <v>12.56733989715576</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>10.81545352935791</v>
+        <v>10.81545639038086</v>
       </c>
       <c r="C60" t="n">
         <v>12.26430988311768</v>
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>11.26826572418213</v>
+        <v>11.2682638168335</v>
       </c>
       <c r="C62" t="n">
         <v>12.77777767181396</v>
@@ -1759,11 +1771,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.43740367889404</v>
+        <v>12.43740177154541</v>
       </c>
       <c r="C63" t="n">
         <v>14.10353469848633</v>
@@ -1788,11 +1800,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.52064990997314</v>
+        <v>11.52065181732178</v>
       </c>
       <c r="C64" t="n">
         <v>13.06397342681885</v>
@@ -1817,11 +1829,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>12.76401996612549</v>
+        <v>12.76401615142822</v>
       </c>
       <c r="C65" t="n">
         <v>14.47390556335449</v>
@@ -1846,11 +1858,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>11.56889724731445</v>
+        <v>11.56889820098877</v>
       </c>
       <c r="C66" t="n">
         <v>13.11868667602539</v>
@@ -1875,11 +1887,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>11.97717094421387</v>
+        <v>11.97716999053955</v>
       </c>
       <c r="C67" t="n">
         <v>13.58164978027344</v>
@@ -1904,11 +1916,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.15532398223877</v>
+        <v>12.15532207489014</v>
       </c>
       <c r="C68" t="n">
         <v>13.78367042541504</v>
@@ -1933,11 +1945,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.45755004882812</v>
+        <v>11.45755386352539</v>
       </c>
       <c r="C69" t="n">
         <v>12.99242401123047</v>
@@ -1962,7 +1974,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1991,7 +2003,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2020,11 +2032,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>10.98247528076172</v>
+        <v>10.98247814178467</v>
       </c>
       <c r="C72" t="n">
         <v>12.45370388031006</v>
@@ -2049,11 +2061,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.25712966918945</v>
+        <v>11.25712871551514</v>
       </c>
       <c r="C73" t="n">
         <v>12.76515197753906</v>
@@ -2078,11 +2090,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.72849941253662</v>
+        <v>11.72849369049072</v>
       </c>
       <c r="C74" t="n">
         <v>13.29966259002686</v>
@@ -2107,11 +2119,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.26507949829102</v>
+        <v>13.26507568359375</v>
       </c>
       <c r="C75" t="n">
         <v>15.04208755493164</v>
@@ -2136,7 +2148,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>15.22477340698242</v>
+        <v>15.22477722167969</v>
       </c>
       <c r="C77" t="n">
         <v>17.26431083679199</v>
@@ -2194,11 +2206,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.54556369781494</v>
+        <v>14.54556274414062</v>
       </c>
       <c r="C78" t="n">
         <v>16.49410820007324</v>
@@ -2223,7 +2235,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2252,11 +2264,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.44215965270996</v>
+        <v>16.44216156005859</v>
       </c>
       <c r="C80" t="n">
         <v>18.6447811126709</v>
@@ -2281,11 +2293,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>17.61872100830078</v>
+        <v>17.61872291564941</v>
       </c>
       <c r="C81" t="n">
         <v>19.97895622253418</v>
@@ -2310,11 +2322,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.95276641845703</v>
+        <v>17.95276260375977</v>
       </c>
       <c r="C82" t="n">
         <v>20.35774421691895</v>
@@ -2339,11 +2351,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.91193389892578</v>
+        <v>17.91193962097168</v>
       </c>
       <c r="C83" t="n">
         <v>20.31144714355469</v>
@@ -2368,11 +2380,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.60440826416016</v>
+        <v>19.60440444946289</v>
       </c>
       <c r="C84" t="n">
         <v>22.23064041137695</v>
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>18.92890548706055</v>
+        <v>18.92889595031738</v>
       </c>
       <c r="C85" t="n">
         <v>21.46464538574219</v>
@@ -2426,11 +2438,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>20.7735424041748</v>
+        <v>20.77353858947754</v>
       </c>
       <c r="C86" t="n">
         <v>23.556396484375</v>
@@ -2455,7 +2467,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>20.1240177154541</v>
+        <v>20.1240234375</v>
       </c>
       <c r="C88" t="n">
         <v>22.81986427307129</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>19.4448127746582</v>
+        <v>19.44480133056641</v>
       </c>
       <c r="C89" t="n">
         <v>22.04966354370117</v>
@@ -2542,7 +2554,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>19.19613075256348</v>
+        <v>19.19613456726074</v>
       </c>
       <c r="C91" t="n">
         <v>21.76767730712891</v>
@@ -2600,11 +2612,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>19.18499755859375</v>
+        <v>19.18499946594238</v>
       </c>
       <c r="C92" t="n">
         <v>21.75505065917969</v>
@@ -2629,11 +2641,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>18.55403709411621</v>
+        <v>18.55403327941895</v>
       </c>
       <c r="C93" t="n">
         <v>21.0395622253418</v>
@@ -2658,7 +2670,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2687,11 +2699,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>19.56357002258301</v>
+        <v>19.56357192993164</v>
       </c>
       <c r="C95" t="n">
         <v>22.1843433380127</v>
@@ -2716,11 +2728,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>18.75074768066406</v>
+        <v>18.75075149536133</v>
       </c>
       <c r="C96" t="n">
         <v>21.26262664794922</v>
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>20.36527061462402</v>
+        <v>20.36527442932129</v>
       </c>
       <c r="C97" t="n">
         <v>23.09343338012695</v>
@@ -2774,11 +2786,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>19.74544334411621</v>
+        <v>19.74544525146484</v>
       </c>
       <c r="C98" t="n">
         <v>22.39057159423828</v>
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>21.81277275085449</v>
+        <v>21.81277465820312</v>
       </c>
       <c r="C99" t="n">
         <v>24.73484802246094</v>
@@ -2832,11 +2844,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>20.50259590148926</v>
+        <v>20.50260543823242</v>
       </c>
       <c r="C100" t="n">
         <v>23.24915885925293</v>
@@ -2861,7 +2873,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2890,11 +2902,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.82868957519531</v>
+        <v>18.82868576049805</v>
       </c>
       <c r="C102" t="n">
         <v>21.35100936889648</v>
@@ -2917,11 +2929,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.58001136779785</v>
+        <v>18.58001327514648</v>
       </c>
       <c r="C103" t="n">
         <v>21.06902313232422</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.60811042785645</v>
+        <v>19.60811996459961</v>
       </c>
       <c r="C104" t="n">
         <v>22.23484802246094</v>
@@ -2971,11 +2983,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>20.59909439086914</v>
+        <v>20.59909820556641</v>
       </c>
       <c r="C105" t="n">
         <v>23.35858535766602</v>
@@ -2998,11 +3010,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>21.01850318908691</v>
+        <v>21.01850700378418</v>
       </c>
       <c r="C106" t="n">
         <v>23.83417510986328</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>19.48563385009766</v>
+        <v>19.48563766479492</v>
       </c>
       <c r="C107" t="n">
         <v>22.09596061706543</v>
@@ -3052,11 +3064,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>20.36898422241211</v>
+        <v>20.36898040771484</v>
       </c>
       <c r="C108" t="n">
         <v>23.09764289855957</v>
@@ -3079,7 +3091,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.67121505737305</v>
+        <v>19.67120933532715</v>
       </c>
       <c r="C110" t="n">
         <v>22.306396484375</v>
@@ -3133,11 +3145,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>21.49358367919922</v>
+        <v>21.49358749389648</v>
       </c>
       <c r="C111" t="n">
         <v>24.37289619445801</v>
@@ -3162,11 +3174,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>21.40821075439453</v>
+        <v>21.4082145690918</v>
       </c>
       <c r="C112" t="n">
         <v>24.27609443664551</v>
@@ -3191,11 +3203,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>21.62348937988281</v>
+        <v>21.62348365783691</v>
       </c>
       <c r="C113" t="n">
         <v>24.52020263671875</v>
@@ -3220,11 +3232,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>22.7740650177002</v>
+        <v>22.77407073974609</v>
       </c>
       <c r="C114" t="n">
         <v>25.82491683959961</v>
@@ -3249,7 +3261,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3278,11 +3290,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>24.79802131652832</v>
+        <v>24.79801940917969</v>
       </c>
       <c r="C116" t="n">
         <v>28.1200008392334</v>
@@ -3307,11 +3319,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>23.90734100341797</v>
+        <v>23.90733337402344</v>
       </c>
       <c r="C117" t="n">
         <v>27.11000061035156</v>
@@ -3336,7 +3348,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3365,11 +3377,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.6040096282959</v>
+        <v>24.60400772094727</v>
       </c>
       <c r="C119" t="n">
         <v>27.89999961853027</v>
@@ -3394,7 +3406,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3423,11 +3435,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>24.23362350463867</v>
+        <v>24.2336254119873</v>
       </c>
       <c r="C121" t="n">
         <v>27.47999954223633</v>
@@ -3452,11 +3464,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>20.68853569030762</v>
+        <v>20.68853378295898</v>
       </c>
       <c r="C122" t="n">
         <v>23.45999908447266</v>
@@ -3481,11 +3493,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.98836708068848</v>
+        <v>20.98836517333984</v>
       </c>
       <c r="C123" t="n">
         <v>23.79999923706055</v>
@@ -3510,11 +3522,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.04127502441406</v>
+        <v>21.04128265380859</v>
       </c>
       <c r="C124" t="n">
         <v>23.86000061035156</v>
@@ -3539,11 +3551,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>21.54393577575684</v>
+        <v>21.54394149780273</v>
       </c>
       <c r="C125" t="n">
         <v>24.43000030517578</v>
@@ -3568,11 +3580,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>21.57039451599121</v>
+        <v>21.57039642333984</v>
       </c>
       <c r="C126" t="n">
         <v>24.45999908447266</v>
@@ -3597,7 +3609,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3626,11 +3638,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>27.47888565063477</v>
+        <v>27.47888946533203</v>
       </c>
       <c r="C128" t="n">
         <v>31.15999984741211</v>
@@ -3655,11 +3667,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>28.36074638366699</v>
+        <v>28.36075401306152</v>
       </c>
       <c r="C129" t="n">
         <v>32.15999984741211</v>
@@ -3684,11 +3696,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>29.01333427429199</v>
+        <v>29.01333618164062</v>
       </c>
       <c r="C130" t="n">
         <v>32.90000152587891</v>
@@ -3713,11 +3725,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.14194679260254</v>
+        <v>25.14194869995117</v>
       </c>
       <c r="C131" t="n">
         <v>28.51000022888184</v>
@@ -3742,11 +3754,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>24.52463912963867</v>
+        <v>24.52464485168457</v>
       </c>
       <c r="C132" t="n">
         <v>27.80999946594238</v>
@@ -3771,11 +3783,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.18254470825195</v>
+        <v>26.18254661560059</v>
       </c>
       <c r="C133" t="n">
         <v>29.69000053405762</v>
@@ -3800,11 +3812,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.06974029541016</v>
+        <v>28.06973266601562</v>
       </c>
       <c r="C134" t="n">
         <v>31.82999992370605</v>
@@ -3829,11 +3841,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.89519500732422</v>
+        <v>29.89519882202148</v>
       </c>
       <c r="C135" t="n">
         <v>33.90000152587891</v>
@@ -3858,11 +3870,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>29.60418319702148</v>
+        <v>29.60418128967285</v>
       </c>
       <c r="C136" t="n">
         <v>33.56999969482422</v>
@@ -3887,11 +3899,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.46307563781738</v>
+        <v>29.46306610107422</v>
       </c>
       <c r="C137" t="n">
         <v>33.40999984741211</v>
@@ -3916,11 +3928,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.2479362487793</v>
+        <v>30.24794387817383</v>
       </c>
       <c r="C138" t="n">
         <v>34.29999923706055</v>
@@ -3945,11 +3957,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>30.79470252990723</v>
+        <v>30.7946891784668</v>
       </c>
       <c r="C139" t="n">
         <v>34.91999816894531</v>
@@ -3974,11 +3986,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>31.50901412963867</v>
+        <v>31.50900077819824</v>
       </c>
       <c r="C140" t="n">
         <v>35.72999954223633</v>
@@ -4003,11 +4015,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.86175155639648</v>
+        <v>31.86174964904785</v>
       </c>
       <c r="C141" t="n">
         <v>36.13000106811523</v>
@@ -4032,11 +4044,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>33.91650009155273</v>
+        <v>33.9164924621582</v>
       </c>
       <c r="C142" t="n">
         <v>38.45999908447266</v>
@@ -4061,11 +4073,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>33.1933708190918</v>
+        <v>33.193359375</v>
       </c>
       <c r="C143" t="n">
         <v>37.63999938964844</v>
@@ -4090,11 +4102,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>30.5742301940918</v>
+        <v>30.57422828674316</v>
       </c>
       <c r="C144" t="n">
         <v>34.66999816894531</v>
@@ -4119,7 +4131,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4148,11 +4160,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.78604507446289</v>
+        <v>35.78605270385742</v>
       </c>
       <c r="C146" t="n">
         <v>40.58000183105469</v>
@@ -4177,11 +4189,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>37.79668807983398</v>
+        <v>37.79669570922852</v>
       </c>
       <c r="C147" t="n">
         <v>42.86000061035156</v>
@@ -4204,11 +4216,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>35.48621368408203</v>
+        <v>35.4862060546875</v>
       </c>
       <c r="C148" t="n">
         <v>40.2400016784668</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.40501403808594</v>
+        <v>33.4050178527832</v>
       </c>
       <c r="C149" t="n">
         <v>37.88000106811523</v>
@@ -4258,11 +4270,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.26392364501953</v>
+        <v>33.2639045715332</v>
       </c>
       <c r="C150" t="n">
         <v>37.72000122070312</v>
@@ -4285,11 +4297,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>31.97639656066895</v>
+        <v>31.97639274597168</v>
       </c>
       <c r="C151" t="n">
         <v>36.2599983215332</v>
@@ -4312,11 +4324,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>29.49835205078125</v>
+        <v>29.49835968017578</v>
       </c>
       <c r="C152" t="n">
         <v>33.45000076293945</v>
@@ -4339,11 +4351,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>30.52131652832031</v>
+        <v>30.52131462097168</v>
       </c>
       <c r="C153" t="n">
         <v>34.61000061035156</v>
@@ -4366,11 +4378,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>29.11915588378906</v>
+        <v>29.1191463470459</v>
       </c>
       <c r="C154" t="n">
         <v>33.02000045776367</v>
@@ -4393,11 +4405,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>25.60051345825195</v>
+        <v>25.60051536560059</v>
       </c>
       <c r="C155" t="n">
         <v>29.03000068664551</v>
@@ -4420,11 +4432,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>26.32364654541016</v>
+        <v>26.32364273071289</v>
       </c>
       <c r="C156" t="n">
         <v>29.85000038146973</v>
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4474,11 +4486,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>29.67473030090332</v>
+        <v>29.67473220825195</v>
       </c>
       <c r="C158" t="n">
         <v>33.65000152587891</v>
@@ -4503,11 +4515,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>32.88376235961914</v>
+        <v>32.88375854492188</v>
       </c>
       <c r="C159" t="n">
         <v>37.15000152587891</v>
@@ -4532,11 +4544,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>32.87490844726562</v>
+        <v>32.87491226196289</v>
       </c>
       <c r="C160" t="n">
         <v>37.13999938964844</v>
@@ -4561,11 +4573,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>34.29999923706055</v>
+        <v>34.30001068115234</v>
       </c>
       <c r="C161" t="n">
         <v>38.75</v>
@@ -4590,11 +4602,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>31.92767333984375</v>
+        <v>31.92768287658691</v>
       </c>
       <c r="C162" t="n">
         <v>35.93000030517578</v>
@@ -4619,11 +4631,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>35.10002136230469</v>
+        <v>35.10000610351562</v>
       </c>
       <c r="C163" t="n">
         <v>39.5</v>
@@ -4648,11 +4660,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>36.60175704956055</v>
+        <v>36.60174942016602</v>
       </c>
       <c r="C164" t="n">
         <v>41.18999862670898</v>
@@ -4677,7 +4689,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4706,7 +4718,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4735,11 +4747,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>31.4319953918457</v>
+        <v>31.43199729919434</v>
       </c>
       <c r="C167" t="n">
         <v>35.25</v>
@@ -4764,11 +4776,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>31.79692077636719</v>
+        <v>31.79693222045898</v>
       </c>
       <c r="C168" t="n">
         <v>35.52000045776367</v>
@@ -4793,11 +4805,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>32.3250846862793</v>
+        <v>32.32508850097656</v>
       </c>
       <c r="C169" t="n">
         <v>36.11000061035156</v>
@@ -4822,11 +4834,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>30.04236602783203</v>
+        <v>30.04236793518066</v>
       </c>
       <c r="C170" t="n">
         <v>33.56000137329102</v>
@@ -4851,11 +4863,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>31.15140533447266</v>
+        <v>31.15140724182129</v>
       </c>
       <c r="C171" t="n">
         <v>34.63999938964844</v>
@@ -4880,7 +4892,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4909,11 +4921,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.81872177124023</v>
+        <v>35.81872940063477</v>
       </c>
       <c r="C173" t="n">
         <v>39.83000183105469</v>
@@ -4938,11 +4950,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>41.10235977172852</v>
+        <v>41.10235595703125</v>
       </c>
       <c r="C174" t="n">
         <v>45.54000091552734</v>
@@ -4967,11 +4979,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>47.33901596069336</v>
+        <v>47.33900451660156</v>
       </c>
       <c r="C175" t="n">
         <v>52.45000076293945</v>
@@ -4996,11 +5008,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>49.89323806762695</v>
+        <v>49.89324188232422</v>
       </c>
       <c r="C176" t="n">
         <v>55.27999877929688</v>
@@ -5025,7 +5037,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5054,7 +5066,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5083,11 +5095,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>43.11582183837891</v>
+        <v>43.11580657958984</v>
       </c>
       <c r="C179" t="n">
         <v>47.63000106811523</v>
@@ -5112,11 +5124,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>45.79315185546875</v>
+        <v>45.79315948486328</v>
       </c>
       <c r="C180" t="n">
         <v>50.43000030517578</v>
@@ -5141,11 +5153,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>45.62970352172852</v>
+        <v>45.62970733642578</v>
       </c>
       <c r="C181" t="n">
         <v>50.25</v>
@@ -5170,11 +5182,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>51.31411743164062</v>
+        <v>51.31412124633789</v>
       </c>
       <c r="C182" t="n">
         <v>56.5099983215332</v>
@@ -5199,11 +5211,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>51.39475250244141</v>
+        <v>51.39474868774414</v>
       </c>
       <c r="C183" t="n">
         <v>56.41999816894531</v>
@@ -5228,7 +5240,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5257,11 +5269,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>50.82086944580078</v>
+        <v>50.82086181640625</v>
       </c>
       <c r="C185" t="n">
         <v>55.79000091552734</v>
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5315,11 +5327,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>64.15052795410156</v>
+        <v>64.15053558349609</v>
       </c>
       <c r="C187" t="n">
         <v>70.20999908447266</v>
@@ -5344,11 +5356,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>62.32313919067383</v>
+        <v>62.32312774658203</v>
       </c>
       <c r="C188" t="n">
         <v>68.20999908447266</v>
@@ -5373,11 +5385,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>70.28007507324219</v>
+        <v>70.28008270263672</v>
       </c>
       <c r="C189" t="n">
         <v>76.73999786376953</v>
@@ -5402,11 +5414,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>63.80523300170898</v>
+        <v>63.80525207519531</v>
       </c>
       <c r="C190" t="n">
         <v>69.66999816894531</v>
@@ -5431,11 +5443,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>70.26177978515625</v>
+        <v>70.26177215576172</v>
       </c>
       <c r="C191" t="n">
         <v>76.72000122070312</v>
@@ -5460,11 +5472,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>61.93929672241211</v>
+        <v>61.93930435180664</v>
       </c>
       <c r="C192" t="n">
         <v>67.45999908447266</v>
@@ -5489,7 +5501,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5518,11 +5530,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>55.15407180786133</v>
+        <v>55.15407943725586</v>
       </c>
       <c r="C194" t="n">
         <v>60.06999969482422</v>
@@ -5547,11 +5559,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>50.12254333496094</v>
+        <v>50.12253570556641</v>
       </c>
       <c r="C195" t="n">
         <v>54.59000015258789</v>
@@ -5576,7 +5588,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5605,11 +5617,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>47.86857986450195</v>
+        <v>47.86858367919922</v>
       </c>
       <c r="C197" t="n">
         <v>51.91999816894531</v>
@@ -5634,11 +5646,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>45.07531356811523</v>
+        <v>45.0753173828125</v>
       </c>
       <c r="C198" t="n">
         <v>48.66999816894531</v>
@@ -5663,11 +5675,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.59231185913086</v>
+        <v>38.59231948852539</v>
       </c>
       <c r="C199" t="n">
         <v>41.66999816894531</v>
@@ -5692,11 +5704,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>45.03826904296875</v>
+        <v>45.03826522827148</v>
       </c>
       <c r="C200" t="n">
         <v>48.63000106811523</v>
@@ -5721,11 +5733,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>41.07392501831055</v>
+        <v>41.07392120361328</v>
       </c>
       <c r="C201" t="n">
         <v>44.13000106811523</v>
@@ -5750,11 +5762,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.26085662841797</v>
+        <v>34.2608528137207</v>
       </c>
       <c r="C202" t="n">
         <v>36.81000137329102</v>
@@ -5779,7 +5791,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5808,11 +5820,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>42.5068473815918</v>
+        <v>42.50685501098633</v>
       </c>
       <c r="C204" t="n">
         <v>45.43999862670898</v>
@@ -5835,11 +5847,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>38.79311370849609</v>
+        <v>38.79311752319336</v>
       </c>
       <c r="C205" t="n">
         <v>41.47000122070312</v>
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5889,11 +5901,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>42.93716049194336</v>
+        <v>42.93715286254883</v>
       </c>
       <c r="C207" t="n">
         <v>45.90000152587891</v>
@@ -5916,11 +5928,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>41.74170303344727</v>
+        <v>41.74169921875</v>
       </c>
       <c r="C208" t="n">
         <v>44.36999893188477</v>
@@ -5943,7 +5955,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5972,11 +5984,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>40.25079727172852</v>
+        <v>40.25078964233398</v>
       </c>
       <c r="C210" t="n">
         <v>42.54000091552734</v>
@@ -6001,11 +6013,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>42.28508758544922</v>
+        <v>42.28509140014648</v>
       </c>
       <c r="C211" t="n">
         <v>44.68999862670898</v>
@@ -6030,7 +6042,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6059,11 +6071,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>42.60828399658203</v>
+        <v>42.60828018188477</v>
       </c>
       <c r="C213" t="n">
         <v>44.77999877929688</v>
@@ -6088,7 +6100,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6117,7 +6129,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6146,7 +6158,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6175,7 +6187,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6204,7 +6216,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6233,7 +6245,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6262,7 +6274,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6291,11 +6303,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>49.60774993896484</v>
+        <v>49.60774612426758</v>
       </c>
       <c r="C221" t="n">
         <v>51.54000091552734</v>
@@ -6320,11 +6332,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>52.45273971557617</v>
+        <v>52.45273208618164</v>
       </c>
       <c r="C222" t="n">
         <v>54.22000122070312</v>
@@ -6349,11 +6361,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>51.96903228759766</v>
+        <v>51.96902847290039</v>
       </c>
       <c r="C223" t="n">
         <v>53.72000122070312</v>
@@ -6378,11 +6390,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>53.79742431640625</v>
+        <v>53.79742813110352</v>
       </c>
       <c r="C224" t="n">
         <v>55.61000061035156</v>
@@ -6407,11 +6419,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>57.43832015991211</v>
+        <v>57.43831634521484</v>
       </c>
       <c r="C225" t="n">
         <v>59.09999847412109</v>
@@ -6436,11 +6448,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>63.27933120727539</v>
+        <v>63.27933883666992</v>
       </c>
       <c r="C226" t="n">
         <v>65.11000061035156</v>
@@ -6465,11 +6477,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>55.89302062988281</v>
+        <v>55.89302444458008</v>
       </c>
       <c r="C227" t="n">
         <v>57.5099983215332</v>
@@ -6494,11 +6506,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>61.76984786987305</v>
+        <v>61.76984405517578</v>
       </c>
       <c r="C228" t="n">
         <v>63.29000091552734</v>
@@ -6523,11 +6535,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>60.46203994750977</v>
+        <v>60.4620361328125</v>
       </c>
       <c r="C229" t="n">
         <v>61.95000076293945</v>
@@ -6552,7 +6564,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6581,7 +6593,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6610,11 +6622,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>66.40292358398438</v>
+        <v>66.40291595458984</v>
       </c>
       <c r="C232" t="n">
         <v>67.73000335693359</v>
@@ -6639,11 +6651,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>66.82450866699219</v>
+        <v>66.82450103759766</v>
       </c>
       <c r="C233" t="n">
         <v>68.16000366210938</v>
@@ -6668,11 +6680,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>72.02347564697266</v>
+        <v>72.02346801757812</v>
       </c>
       <c r="C234" t="n">
         <v>73.16999816894531</v>
@@ -6697,7 +6709,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6726,7 +6738,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6755,11 +6767,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>89.46979522705078</v>
+        <v>89.46978759765625</v>
       </c>
       <c r="C237" t="n">
         <v>90.61000061035156</v>
@@ -6784,7 +6796,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6813,11 +6825,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>80.28681945800781</v>
+        <v>80.28681182861328</v>
       </c>
       <c r="C239" t="n">
         <v>81.30999755859375</v>
@@ -6842,7 +6854,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6871,7 +6883,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6900,11 +6912,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>90.389892578125</v>
+        <v>90.38990020751953</v>
       </c>
       <c r="C242" t="n">
         <v>91.22000122070312</v>
@@ -6929,7 +6941,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6958,7 +6970,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6987,7 +6999,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7016,7 +7028,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7045,7 +7057,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7074,7 +7086,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7103,7 +7115,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7132,32 +7144,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>109.0899963378906</v>
+        <v>107.8300018310547</v>
       </c>
       <c r="C250" t="n">
-        <v>109.0899963378906</v>
+        <v>107.8300018310547</v>
       </c>
       <c r="D250" t="n">
-        <v>89804600</v>
+        <v>93033500</v>
       </c>
       <c r="E250" t="n">
         <v>4.820000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>22.63277932321382</v>
+        <v>22.37136967449267</v>
       </c>
       <c r="G250" t="n">
         <v>445000000</v>
       </c>
       <c r="H250" t="n">
-        <v>48545048370.36133</v>
+        <v>47984350814.81934</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2018080898876405</v>
+        <v>0.2090640449438202</v>
       </c>
     </row>
   </sheetData>
@@ -7189,75 +7201,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7293,13 +7305,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7335,13 +7347,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7377,13 +7389,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7419,13 +7431,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7461,13 +7473,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7494,7 +7506,7 @@
       <c r="I7" t="n">
         <v>0.765993265993266</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K7" t="n">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I8" t="n">
         <v>0.7744107744107744</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K8" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I9" t="n">
         <v>0.7996632996632997</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K9" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40472</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I10" t="n">
         <v>0.824915824915825</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K10" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I11" t="n">
         <v>0.5723905723905724</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K11" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I12" t="n">
         <v>0.5976430976430976</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="K12" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I13" t="n">
         <v>0.5597643097643098</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="K13" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I14" t="n">
         <v>0.5765993265993266</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="K14" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I15" t="n">
         <v>1.035353535353535</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="K15" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41019</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I16" t="n">
         <v>1.069023569023569</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41019</v>
       </c>
       <c r="K16" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I17" t="n">
         <v>1.19949494949495</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="K17" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I18" t="n">
         <v>1.233164983164983</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="K18" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I19" t="n">
         <v>0.8375420875420876</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="K19" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I20" t="n">
         <v>0.867003367003367</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="K20" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I21" t="n">
         <v>0.8501683501683501</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="K21" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I22" t="n">
         <v>0.8838383838383839</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="K22" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I23" t="n">
         <v>0.9175084175084176</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="K23" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I24" t="n">
         <v>-0.06313131313131304</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K24" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41838</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I25" t="n">
         <v>-0.04629629629629622</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41838</v>
       </c>
       <c r="K25" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I26" t="n">
         <v>-0.04208754208754201</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="K26" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I27" t="n">
         <v>0.02946127946127952</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="K27" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I28" t="n">
         <v>1.01010101010101</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K28" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I29" t="n">
         <v>0.8570370370370372</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="K29" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I30" t="n">
         <v>1.07976430976431</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K30" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I31" t="n">
         <v>1.124646464646465</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="K31" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I32" t="n">
         <v>1.32</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I33" t="n">
         <v>1.63</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="K33" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I34" t="n">
         <v>1.54</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K34" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I35" t="n">
         <v>6.449999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="K35" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I36" t="n">
         <v>6.98</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="K36" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I37" t="n">
         <v>6.62</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="K37" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I38" t="n">
         <v>6.74</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="K38" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43136</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I39" t="n">
         <v>-1.069999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43136</v>
       </c>
       <c r="K39" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I40" t="n">
         <v>-1.609999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I41" t="n">
         <v>-0.9899999999999989</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="K41" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I42" t="n">
         <v>-0.7399999999999989</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K42" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I43" t="n">
         <v>2.570000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="K43" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I44" t="n">
         <v>2.740000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K44" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I45" t="n">
         <v>2.560000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="K45" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I46" t="n">
         <v>2.200000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K46" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I47" t="n">
         <v>2.090000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="K47" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I48" t="n">
         <v>6.030000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K48" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I49" t="n">
         <v>6.620000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I50" t="n">
         <v>7.190000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I51" t="n">
         <v>7.710000000000002</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K51" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I52" t="n">
         <v>4.120000000000002</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I53" t="n">
         <v>18.75</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="K53" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I54" t="n">
         <v>18.21</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I55" t="n">
         <v>20.25</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I56" t="n">
         <v>17.05</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K56" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I57" t="n">
         <v>0.4200000000000019</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I58" t="n">
         <v>-0.1099999999999981</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I59" t="n">
         <v>-2.269999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I60" t="n">
         <v>1.060000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I61" t="n">
         <v>2.330000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I62" t="n">
         <v>4.920000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="K62" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I63" t="n">
         <v>5.190000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K63" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I64" t="n">
         <v>4.990000000000002</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I65" t="n">
         <v>5.120000000000002</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I66" t="n">
         <v>3.950000000000002</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I67" t="n">
         <v>3.940000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K67" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I68" t="n">
         <v>4.150000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I69" t="n">
         <v>4.490000000000002</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I70" t="n">
         <v>4.550000000000002</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I71" t="n">
         <v>4.340000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I72" t="n">
         <v>4.400000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K72" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I73" t="n">
         <v>4.820000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K73" t="n">
@@ -10567,52 +10579,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40015</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="C2" t="n">
@@ -10641,10 +10653,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40100</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="C3" t="n">
@@ -10673,10 +10685,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40226</v>
       </c>
       <c r="C4" t="n">
@@ -10705,10 +10717,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40282</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C5" t="n">
@@ -10737,10 +10749,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40374</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10769,10 +10781,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40465</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40472</v>
       </c>
       <c r="C7" t="n">
@@ -10801,10 +10813,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40570</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="C8" t="n">
@@ -10833,10 +10845,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40658</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C9" t="n">
@@ -10865,10 +10877,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40742</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="C10" t="n">
@@ -10897,10 +10909,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40833</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="C11" t="n">
@@ -10929,10 +10941,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40931</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="C12" t="n">
@@ -10961,10 +10973,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41019</v>
       </c>
       <c r="C13" t="n">
@@ -10993,10 +11005,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="C14" t="n">
@@ -11025,10 +11037,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41197</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="C15" t="n">
@@ -11057,10 +11069,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41302</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="C16" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41379</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="C17" t="n">
@@ -11121,10 +11133,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41470</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="C18" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41561</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="C19" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41663</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="C20" t="n">
@@ -11217,10 +11229,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C21" t="n">
@@ -11249,10 +11261,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41831</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41838</v>
       </c>
       <c r="C22" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41922</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41928</v>
       </c>
       <c r="C23" t="n">
@@ -11313,10 +11325,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42037</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="C24" t="n">
@@ -11345,10 +11357,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42114</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C25" t="n">
@@ -11377,10 +11389,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42199</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="C26" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11441,10 +11453,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42396</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="C28" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11505,10 +11517,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42570</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="C30" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42661</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C31" t="n">
@@ -11569,10 +11581,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="C32" t="n">
@@ -11601,10 +11613,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42842</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="C33" t="n">
@@ -11633,10 +11645,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="C34" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43024</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="C35" t="n">
@@ -11697,10 +11709,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43136</v>
       </c>
       <c r="C36" t="n">
@@ -11729,10 +11741,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43213</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43297</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="C38" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11825,10 +11837,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="C40" t="n">
@@ -11857,10 +11869,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43577</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11889,10 +11901,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43661</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="C42" t="n">
@@ -11921,10 +11933,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C43" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43857</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="C44" t="n">
@@ -11985,10 +11997,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43936</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -12017,10 +12029,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C46" t="n">
@@ -12049,10 +12061,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C47" t="n">
@@ -12081,10 +12093,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C48" t="n">
@@ -12113,10 +12125,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C49" t="n">
@@ -12145,10 +12157,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44312</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C50" t="n">
@@ -12177,10 +12189,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44417</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="C51" t="n">
@@ -12209,10 +12221,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44494</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C52" t="n">
@@ -12241,10 +12253,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44613</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C53" t="n">
@@ -12273,10 +12285,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C54" t="n">
@@ -12305,10 +12317,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C55" t="n">
@@ -12337,10 +12349,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C56" t="n">
@@ -12369,10 +12381,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44978</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C57" t="n">
@@ -12401,10 +12413,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C58" t="n">
@@ -12433,10 +12445,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45055</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="C59" t="n">
@@ -12465,10 +12477,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C60" t="n">
@@ -12497,10 +12509,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="C61" t="n">
@@ -12529,10 +12541,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45345</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C62" t="n">
@@ -12561,10 +12573,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C63" t="n">
@@ -12593,10 +12605,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="C64" t="n">
@@ -12625,10 +12637,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C65" t="n">
@@ -12657,10 +12669,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C66" t="n">
@@ -12689,10 +12701,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C67" t="n">
@@ -12721,10 +12733,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C68" t="n">
@@ -12753,10 +12765,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45803</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="C69" t="n">
@@ -12785,10 +12797,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C70" t="n">
@@ -12817,10 +12829,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C71" t="n">
@@ -12849,10 +12861,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C72" t="n">
@@ -12881,10 +12893,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C73" t="n">
@@ -12913,10 +12925,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C74" t="n">
@@ -12963,12 +12975,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -13039,7 +13051,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/EBAY.xlsx
+++ b/salidas/empresas/EBAY.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.99677562713623</v>
+        <v>15.9967794418335</v>
       </c>
       <c r="C2" t="n">
         <v>18.13973045349121</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.47504234313965</v>
+        <v>14.47504043579102</v>
       </c>
       <c r="C4" t="n">
         <v>16.41414070129395</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.77144145965576</v>
+        <v>12.77144050598145</v>
       </c>
       <c r="C5" t="n">
         <v>14.48232269287109</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.1775951385498</v>
+        <v>12.17759323120117</v>
       </c>
       <c r="C6" t="n">
         <v>13.80892276763916</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.87112903594971</v>
+        <v>10.87112522125244</v>
       </c>
       <c r="C7" t="n">
         <v>12.32744121551514</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>8.933697700500488</v>
+        <v>8.933698654174805</v>
       </c>
       <c r="C8" t="n">
         <v>10.13047122955322</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.32553005218506</v>
+        <v>10.32553100585938</v>
       </c>
       <c r="C9" t="n">
         <v>11.70875358581543</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.92521095275879</v>
+        <v>11.92520618438721</v>
       </c>
       <c r="C11" t="n">
         <v>13.52272701263428</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.16062641143799</v>
+        <v>11.16062927246094</v>
       </c>
       <c r="C13" t="n">
         <v>12.65572357177734</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.02171039581299</v>
+        <v>12.02170658111572</v>
       </c>
       <c r="C14" t="n">
         <v>13.632155418396</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.89922618865967</v>
+        <v>11.8992280960083</v>
       </c>
       <c r="C15" t="n">
         <v>13.49326610565186</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>12.303786277771</v>
+        <v>12.30378532409668</v>
       </c>
       <c r="C16" t="n">
         <v>13.95201969146729</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>12.08480358123779</v>
+        <v>12.08480644226074</v>
       </c>
       <c r="C18" t="n">
         <v>13.70370388031006</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>11.94376373291016</v>
+        <v>11.94376659393311</v>
       </c>
       <c r="C19" t="n">
         <v>13.5437707901001</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.02542114257812</v>
+        <v>12.02542304992676</v>
       </c>
       <c r="C20" t="n">
         <v>13.6363639831543</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.6563835144043</v>
+        <v>12.65638542175293</v>
       </c>
       <c r="C21" t="n">
         <v>14.35185241699219</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>13.39869403839111</v>
+        <v>13.3986930847168</v>
       </c>
       <c r="C23" t="n">
         <v>15.19360256195068</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>12.31863307952881</v>
+        <v>12.31863403320312</v>
       </c>
       <c r="C25" t="n">
         <v>13.9688549041748</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>11.61344051361084</v>
+        <v>11.61343669891357</v>
       </c>
       <c r="C29" t="n">
         <v>13.16919231414795</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.13835716247559</v>
+        <v>11.13836002349854</v>
       </c>
       <c r="C30" t="n">
         <v>12.63047122955322</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.14366149902344</v>
+        <v>10.14366340637207</v>
       </c>
       <c r="C31" t="n">
         <v>11.50252532958984</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>9.252895355224609</v>
+        <v>9.25289249420166</v>
       </c>
       <c r="C33" t="n">
         <v>10.49242401123047</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>8.306448936462402</v>
+        <v>8.306447982788086</v>
       </c>
       <c r="C34" t="n">
         <v>9.419192314147949</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.667535781860352</v>
+        <v>5.667537212371826</v>
       </c>
       <c r="C35" t="n">
         <v>6.426767826080322</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>4.873263359069824</v>
+        <v>4.873264789581299</v>
       </c>
       <c r="C36" t="n">
         <v>5.52609395980835</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.181323051452637</v>
+        <v>5.181321144104004</v>
       </c>
       <c r="C37" t="n">
         <v>5.875421047210693</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.461283206939697</v>
+        <v>4.461282253265381</v>
       </c>
       <c r="C38" t="n">
         <v>5.05892276763916</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>4.034453392028809</v>
+        <v>4.034454345703125</v>
       </c>
       <c r="C39" t="n">
         <v>4.574915885925293</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>4.66170597076416</v>
+        <v>4.661706447601318</v>
       </c>
       <c r="C40" t="n">
         <v>5.286194801330566</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>6.112922191619873</v>
+        <v>6.112922668457031</v>
       </c>
       <c r="C41" t="n">
         <v>6.931818008422852</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>6.539749145507812</v>
+        <v>6.539750576019287</v>
       </c>
       <c r="C42" t="n">
         <v>7.415824890136719</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>6.357882976531982</v>
+        <v>6.357884883880615</v>
       </c>
       <c r="C43" t="n">
         <v>7.209596157073975</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.88704252243042</v>
+        <v>7.887041568756104</v>
       </c>
       <c r="C44" t="n">
         <v>8.943602561950684</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>8.217369079589844</v>
+        <v>8.21737003326416</v>
       </c>
       <c r="C45" t="n">
         <v>9.318181991577148</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>8.265619277954102</v>
+        <v>8.265620231628418</v>
       </c>
       <c r="C47" t="n">
         <v>9.372896194458008</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>9.082161903381348</v>
+        <v>9.082164764404297</v>
       </c>
       <c r="C48" t="n">
         <v>10.2988224029541</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.733278274536133</v>
+        <v>8.733273506164551</v>
       </c>
       <c r="C49" t="n">
         <v>9.903199195861816</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.543986320495605</v>
+        <v>8.543987274169922</v>
       </c>
       <c r="C50" t="n">
         <v>9.688551902770996</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.543986320495605</v>
+        <v>8.543987274169922</v>
       </c>
       <c r="C51" t="n">
         <v>9.688551902770996</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>10.01004791259766</v>
+        <v>10.01004695892334</v>
       </c>
       <c r="C52" t="n">
         <v>11.3510103225708</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.946427822113037</v>
+        <v>7.946429252624512</v>
       </c>
       <c r="C54" t="n">
         <v>9.010943412780762</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.278347492218018</v>
+        <v>7.278349876403809</v>
       </c>
       <c r="C55" t="n">
         <v>8.25336742401123</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.621928215026855</v>
+        <v>8.621931076049805</v>
       </c>
       <c r="C57" t="n">
         <v>9.776935577392578</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.056180953979492</v>
+        <v>9.056178092956543</v>
       </c>
       <c r="C58" t="n">
         <v>10.26935958862305</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>10.81545639038086</v>
+        <v>10.81545829772949</v>
       </c>
       <c r="C60" t="n">
         <v>12.26430988311768</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>10.32924175262451</v>
+        <v>10.32924461364746</v>
       </c>
       <c r="C61" t="n">
         <v>11.71296310424805</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>11.2682638168335</v>
+        <v>11.26826286315918</v>
       </c>
       <c r="C62" t="n">
         <v>12.77777767181396</v>
@@ -1775,7 +1775,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.43740177154541</v>
+        <v>12.43740081787109</v>
       </c>
       <c r="C63" t="n">
         <v>14.10353469848633</v>
@@ -1804,7 +1804,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.52065181732178</v>
+        <v>11.52064800262451</v>
       </c>
       <c r="C64" t="n">
         <v>13.06397342681885</v>
@@ -1833,7 +1833,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>12.76401615142822</v>
+        <v>12.76401901245117</v>
       </c>
       <c r="C65" t="n">
         <v>14.47390556335449</v>
@@ -1862,7 +1862,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>11.56889820098877</v>
+        <v>11.56889629364014</v>
       </c>
       <c r="C66" t="n">
         <v>13.11868667602539</v>
@@ -1920,7 +1920,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>12.15532207489014</v>
+        <v>12.15532493591309</v>
       </c>
       <c r="C68" t="n">
         <v>13.78367042541504</v>
@@ -1949,7 +1949,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>11.45755386352539</v>
+        <v>11.45755195617676</v>
       </c>
       <c r="C69" t="n">
         <v>12.99242401123047</v>
@@ -1978,7 +1978,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>10.94536018371582</v>
+        <v>10.9453592300415</v>
       </c>
       <c r="C70" t="n">
         <v>12.41161632537842</v>
@@ -2007,7 +2007,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>11.8138599395752</v>
+        <v>11.81386375427246</v>
       </c>
       <c r="C71" t="n">
         <v>13.39646530151367</v>
@@ -2036,7 +2036,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>10.98247814178467</v>
+        <v>10.98247718811035</v>
       </c>
       <c r="C72" t="n">
         <v>12.45370388031006</v>
@@ -2094,7 +2094,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.72849369049072</v>
+        <v>11.72849273681641</v>
       </c>
       <c r="C74" t="n">
         <v>13.29966259002686</v>
@@ -2123,7 +2123,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.26507568359375</v>
+        <v>13.2650785446167</v>
       </c>
       <c r="C75" t="n">
         <v>15.04208755493164</v>
@@ -2152,7 +2152,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>13.69561672210693</v>
+        <v>13.69561767578125</v>
       </c>
       <c r="C76" t="n">
         <v>15.53030300140381</v>
@@ -2210,7 +2210,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.54556274414062</v>
+        <v>14.54556083679199</v>
       </c>
       <c r="C78" t="n">
         <v>16.49410820007324</v>
@@ -2239,7 +2239,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.5922155380249</v>
+        <v>15.59221935272217</v>
       </c>
       <c r="C79" t="n">
         <v>17.68097686767578</v>
@@ -2268,7 +2268,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.44216156005859</v>
+        <v>16.44216346740723</v>
       </c>
       <c r="C80" t="n">
         <v>18.6447811126709</v>
@@ -2326,7 +2326,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.95276260375977</v>
+        <v>17.95276641845703</v>
       </c>
       <c r="C82" t="n">
         <v>20.35774421691895</v>
@@ -2355,7 +2355,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.91193962097168</v>
+        <v>17.91193771362305</v>
       </c>
       <c r="C83" t="n">
         <v>20.31144714355469</v>
@@ -2413,7 +2413,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>18.92889595031738</v>
+        <v>18.92890167236328</v>
       </c>
       <c r="C85" t="n">
         <v>21.46464538574219</v>
@@ -2442,7 +2442,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>20.77353858947754</v>
+        <v>20.77354431152344</v>
       </c>
       <c r="C86" t="n">
         <v>23.556396484375</v>
@@ -2471,7 +2471,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>20.30588722229004</v>
+        <v>20.3058910369873</v>
       </c>
       <c r="C87" t="n">
         <v>23.02609443664551</v>
@@ -2500,7 +2500,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>20.1240234375</v>
+        <v>20.12402153015137</v>
       </c>
       <c r="C88" t="n">
         <v>22.81986427307129</v>
@@ -2529,7 +2529,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>19.44480133056641</v>
+        <v>19.44480895996094</v>
       </c>
       <c r="C89" t="n">
         <v>22.04966354370117</v>
@@ -2558,7 +2558,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>20.0794792175293</v>
+        <v>20.07948112487793</v>
       </c>
       <c r="C90" t="n">
         <v>22.76935958862305</v>
@@ -2645,7 +2645,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>18.55403327941895</v>
+        <v>18.55403709411621</v>
       </c>
       <c r="C93" t="n">
         <v>21.0395622253418</v>
@@ -2674,7 +2674,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>20.71044158935547</v>
+        <v>20.7104434967041</v>
       </c>
       <c r="C94" t="n">
         <v>23.48484802246094</v>
@@ -2703,7 +2703,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>19.56357192993164</v>
+        <v>19.56357574462891</v>
       </c>
       <c r="C95" t="n">
         <v>22.1843433380127</v>
@@ -2732,7 +2732,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>18.75075149536133</v>
+        <v>18.75074768066406</v>
       </c>
       <c r="C96" t="n">
         <v>21.26262664794922</v>
@@ -2761,7 +2761,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>20.36527442932129</v>
+        <v>20.36526870727539</v>
       </c>
       <c r="C97" t="n">
         <v>23.09343338012695</v>
@@ -2790,7 +2790,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>19.74544525146484</v>
+        <v>19.74543952941895</v>
       </c>
       <c r="C98" t="n">
         <v>22.39057159423828</v>
@@ -2819,7 +2819,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>21.81277465820312</v>
+        <v>21.81277084350586</v>
       </c>
       <c r="C99" t="n">
         <v>24.73484802246094</v>
@@ -2848,7 +2848,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>20.50260543823242</v>
+        <v>20.50260353088379</v>
       </c>
       <c r="C100" t="n">
         <v>23.24915885925293</v>
@@ -2877,7 +2877,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>19.23696517944336</v>
+        <v>19.23696136474609</v>
       </c>
       <c r="C101" t="n">
         <v>21.81397247314453</v>
@@ -2906,7 +2906,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.82868576049805</v>
+        <v>18.82868957519531</v>
       </c>
       <c r="C102" t="n">
         <v>21.35100936889648</v>
@@ -2933,7 +2933,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.58001327514648</v>
+        <v>18.58001708984375</v>
       </c>
       <c r="C103" t="n">
         <v>21.06902313232422</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>19.60811996459961</v>
+        <v>19.60811614990234</v>
       </c>
       <c r="C104" t="n">
         <v>22.23484802246094</v>
@@ -2987,7 +2987,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>20.59909820556641</v>
+        <v>20.59909629821777</v>
       </c>
       <c r="C105" t="n">
         <v>23.35858535766602</v>
@@ -3014,7 +3014,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>21.01850700378418</v>
+        <v>21.01850891113281</v>
       </c>
       <c r="C106" t="n">
         <v>23.83417510986328</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>19.48563766479492</v>
+        <v>19.48563957214355</v>
       </c>
       <c r="C107" t="n">
         <v>22.09596061706543</v>
@@ -3068,7 +3068,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>20.36898040771484</v>
+        <v>20.36898231506348</v>
       </c>
       <c r="C108" t="n">
         <v>23.09764289855957</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>20.82921600341797</v>
+        <v>20.82921409606934</v>
       </c>
       <c r="C109" t="n">
         <v>23.61952972412109</v>
@@ -3122,7 +3122,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>19.67120933532715</v>
+        <v>19.67121315002441</v>
       </c>
       <c r="C110" t="n">
         <v>22.306396484375</v>
@@ -3178,7 +3178,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>21.4082145690918</v>
+        <v>21.40821647644043</v>
       </c>
       <c r="C112" t="n">
         <v>24.27609443664551</v>
@@ -3207,7 +3207,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>21.62348365783691</v>
+        <v>21.62349128723145</v>
       </c>
       <c r="C113" t="n">
         <v>24.52020263671875</v>
@@ -3265,7 +3265,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>22.35837364196777</v>
+        <v>22.35837554931641</v>
       </c>
       <c r="C115" t="n">
         <v>25.35353469848633</v>
@@ -3294,7 +3294,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>24.79801940917969</v>
+        <v>24.79802703857422</v>
       </c>
       <c r="C116" t="n">
         <v>28.1200008392334</v>
@@ -3323,7 +3323,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>23.90733337402344</v>
+        <v>23.90733909606934</v>
       </c>
       <c r="C117" t="n">
         <v>27.11000061035156</v>
@@ -3352,7 +3352,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>21.55275917053223</v>
+        <v>21.55276298522949</v>
       </c>
       <c r="C118" t="n">
         <v>24.44000053405762</v>
@@ -3381,7 +3381,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.60400772094727</v>
+        <v>24.60401344299316</v>
       </c>
       <c r="C119" t="n">
         <v>27.89999961853027</v>
@@ -3410,7 +3410,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>26.09435844421387</v>
+        <v>26.09435653686523</v>
       </c>
       <c r="C120" t="n">
         <v>29.59000015258789</v>
@@ -3439,7 +3439,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>24.2336254119873</v>
+        <v>24.23362922668457</v>
       </c>
       <c r="C121" t="n">
         <v>27.47999954223633</v>
@@ -3468,7 +3468,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>20.68853378295898</v>
+        <v>20.68852996826172</v>
       </c>
       <c r="C122" t="n">
         <v>23.45999908447266</v>
@@ -3497,7 +3497,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.98836517333984</v>
+        <v>20.98836898803711</v>
       </c>
       <c r="C123" t="n">
         <v>23.79999923706055</v>
@@ -3526,7 +3526,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.04128265380859</v>
+        <v>21.04128074645996</v>
       </c>
       <c r="C124" t="n">
         <v>23.86000061035156</v>
@@ -3584,7 +3584,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>21.57039642333984</v>
+        <v>21.57039833068848</v>
       </c>
       <c r="C126" t="n">
         <v>24.45999908447266</v>
@@ -3613,7 +3613,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>20.64444160461426</v>
+        <v>20.64443969726562</v>
       </c>
       <c r="C127" t="n">
         <v>23.40999984741211</v>
@@ -3642,7 +3642,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>27.47888946533203</v>
+        <v>27.47888565063477</v>
       </c>
       <c r="C128" t="n">
         <v>31.15999984741211</v>
@@ -3671,7 +3671,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>28.36075401306152</v>
+        <v>28.36074829101562</v>
       </c>
       <c r="C129" t="n">
         <v>32.15999984741211</v>
@@ -3729,7 +3729,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.14194869995117</v>
+        <v>25.14194679260254</v>
       </c>
       <c r="C131" t="n">
         <v>28.51000022888184</v>
@@ -3758,7 +3758,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>24.52464485168457</v>
+        <v>24.52464294433594</v>
       </c>
       <c r="C132" t="n">
         <v>27.80999946594238</v>
@@ -3787,7 +3787,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.18254661560059</v>
+        <v>26.18254280090332</v>
       </c>
       <c r="C133" t="n">
         <v>29.69000053405762</v>
@@ -3816,7 +3816,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>28.06973266601562</v>
+        <v>28.06973457336426</v>
       </c>
       <c r="C134" t="n">
         <v>31.82999992370605</v>
@@ -3845,7 +3845,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.89519882202148</v>
+        <v>29.89519500732422</v>
       </c>
       <c r="C135" t="n">
         <v>33.90000152587891</v>
@@ -3903,7 +3903,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.46306610107422</v>
+        <v>29.46307563781738</v>
       </c>
       <c r="C137" t="n">
         <v>33.40999984741211</v>
@@ -3932,7 +3932,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.24794387817383</v>
+        <v>30.24794769287109</v>
       </c>
       <c r="C138" t="n">
         <v>34.29999923706055</v>
@@ -3961,7 +3961,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>30.7946891784668</v>
+        <v>30.7946949005127</v>
       </c>
       <c r="C139" t="n">
         <v>34.91999816894531</v>
@@ -3990,7 +3990,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>31.50900077819824</v>
+        <v>31.50900459289551</v>
       </c>
       <c r="C140" t="n">
         <v>35.72999954223633</v>
@@ -4019,7 +4019,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.86174964904785</v>
+        <v>31.86175537109375</v>
       </c>
       <c r="C141" t="n">
         <v>36.13000106811523</v>
@@ -4135,7 +4135,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>33.28155899047852</v>
+        <v>33.28155136108398</v>
       </c>
       <c r="C145" t="n">
         <v>37.7400016784668</v>
@@ -4247,7 +4247,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.4050178527832</v>
+        <v>33.40501403808594</v>
       </c>
       <c r="C149" t="n">
         <v>37.88000106811523</v>
@@ -4274,7 +4274,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.2639045715332</v>
+        <v>33.26391983032227</v>
       </c>
       <c r="C150" t="n">
         <v>37.72000122070312</v>
@@ -4301,7 +4301,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>31.97639274597168</v>
+        <v>31.97640228271484</v>
       </c>
       <c r="C151" t="n">
         <v>36.2599983215332</v>
@@ -4328,7 +4328,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>29.49835968017578</v>
+        <v>29.49835395812988</v>
       </c>
       <c r="C152" t="n">
         <v>33.45000076293945</v>
@@ -4355,7 +4355,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>30.52131462097168</v>
+        <v>30.52132797241211</v>
       </c>
       <c r="C153" t="n">
         <v>34.61000061035156</v>
@@ -4382,7 +4382,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>29.1191463470459</v>
+        <v>29.1191577911377</v>
       </c>
       <c r="C154" t="n">
         <v>33.02000045776367</v>
@@ -4436,7 +4436,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>26.32364273071289</v>
+        <v>26.32364463806152</v>
       </c>
       <c r="C156" t="n">
         <v>29.85000038146973</v>
@@ -4463,7 +4463,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>24.75392532348633</v>
+        <v>24.75392913818359</v>
       </c>
       <c r="C157" t="n">
         <v>28.06999969482422</v>
@@ -4519,7 +4519,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>32.88375854492188</v>
+        <v>32.88375473022461</v>
       </c>
       <c r="C159" t="n">
         <v>37.15000152587891</v>
@@ -4577,7 +4577,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>34.30001068115234</v>
+        <v>34.30002212524414</v>
       </c>
       <c r="C161" t="n">
         <v>38.75</v>
@@ -4635,7 +4635,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>35.10000610351562</v>
+        <v>35.10001373291016</v>
       </c>
       <c r="C163" t="n">
         <v>39.5</v>
@@ -4664,7 +4664,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>36.60174942016602</v>
+        <v>36.60174560546875</v>
       </c>
       <c r="C164" t="n">
         <v>41.18999862670898</v>
@@ -4722,7 +4722,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>34.75799179077148</v>
+        <v>34.75799942016602</v>
       </c>
       <c r="C166" t="n">
         <v>38.97999954223633</v>
@@ -4751,7 +4751,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>31.43199729919434</v>
+        <v>31.43199348449707</v>
       </c>
       <c r="C167" t="n">
         <v>35.25</v>
@@ -4780,7 +4780,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>31.79693222045898</v>
+        <v>31.79692649841309</v>
       </c>
       <c r="C168" t="n">
         <v>35.52000045776367</v>
@@ -4809,7 +4809,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>32.32508850097656</v>
+        <v>32.32508087158203</v>
       </c>
       <c r="C169" t="n">
         <v>36.11000061035156</v>
@@ -4838,7 +4838,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>30.04236793518066</v>
+        <v>30.0423641204834</v>
       </c>
       <c r="C170" t="n">
         <v>33.56000137329102</v>
@@ -4867,7 +4867,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>31.15140724182129</v>
+        <v>31.15140342712402</v>
       </c>
       <c r="C171" t="n">
         <v>34.63999938964844</v>
@@ -4896,7 +4896,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>27.03266334533691</v>
+        <v>27.03265762329102</v>
       </c>
       <c r="C172" t="n">
         <v>30.05999946594238</v>
@@ -4925,7 +4925,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.81872940063477</v>
+        <v>35.8187255859375</v>
       </c>
       <c r="C173" t="n">
         <v>39.83000183105469</v>
@@ -4983,7 +4983,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>47.33900451660156</v>
+        <v>47.33901214599609</v>
       </c>
       <c r="C175" t="n">
         <v>52.45000076293945</v>
@@ -5012,7 +5012,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>49.89324188232422</v>
+        <v>49.89324569702148</v>
       </c>
       <c r="C176" t="n">
         <v>55.27999877929688</v>
@@ -5041,7 +5041,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>49.58816528320312</v>
+        <v>49.58815765380859</v>
       </c>
       <c r="C177" t="n">
         <v>54.77999877929688</v>
@@ -5070,7 +5070,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.16216278076172</v>
+        <v>47.16216659545898</v>
       </c>
       <c r="C178" t="n">
         <v>52.09999847412109</v>
@@ -5099,7 +5099,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>43.11580657958984</v>
+        <v>43.11581039428711</v>
       </c>
       <c r="C179" t="n">
         <v>47.63000106811523</v>
@@ -5128,7 +5128,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>45.79315948486328</v>
+        <v>45.79314804077148</v>
       </c>
       <c r="C180" t="n">
         <v>50.43000030517578</v>
@@ -5157,7 +5157,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>45.62970733642578</v>
+        <v>45.62971115112305</v>
       </c>
       <c r="C181" t="n">
         <v>50.25</v>
@@ -5186,7 +5186,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>51.31412124633789</v>
+        <v>51.31411361694336</v>
       </c>
       <c r="C182" t="n">
         <v>56.5099983215332</v>
@@ -5215,7 +5215,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>51.39474868774414</v>
+        <v>51.39475250244141</v>
       </c>
       <c r="C183" t="n">
         <v>56.41999816894531</v>
@@ -5244,7 +5244,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>55.78544998168945</v>
+        <v>55.78543853759766</v>
       </c>
       <c r="C184" t="n">
         <v>61.2400016784668</v>
@@ -5273,7 +5273,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>50.82086181640625</v>
+        <v>50.82085418701172</v>
       </c>
       <c r="C185" t="n">
         <v>55.79000091552734</v>
@@ -5302,7 +5302,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>55.62575531005859</v>
+        <v>55.62575912475586</v>
       </c>
       <c r="C186" t="n">
         <v>60.88000106811523</v>
@@ -5331,7 +5331,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>64.15053558349609</v>
+        <v>64.15052032470703</v>
       </c>
       <c r="C187" t="n">
         <v>70.20999908447266</v>
@@ -5360,7 +5360,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>62.32312774658203</v>
+        <v>62.32312393188477</v>
       </c>
       <c r="C188" t="n">
         <v>68.20999908447266</v>
@@ -5418,7 +5418,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>63.80525207519531</v>
+        <v>63.80524826049805</v>
       </c>
       <c r="C190" t="n">
         <v>69.66999816894531</v>
@@ -5476,7 +5476,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>61.93930435180664</v>
+        <v>61.93928909301758</v>
       </c>
       <c r="C192" t="n">
         <v>67.45999908447266</v>
@@ -5534,7 +5534,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>55.15407943725586</v>
+        <v>55.15406799316406</v>
       </c>
       <c r="C194" t="n">
         <v>60.06999969482422</v>
@@ -5621,7 +5621,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>47.86858367919922</v>
+        <v>47.86857604980469</v>
       </c>
       <c r="C197" t="n">
         <v>51.91999816894531</v>
@@ -5650,7 +5650,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>45.0753173828125</v>
+        <v>45.07530975341797</v>
       </c>
       <c r="C198" t="n">
         <v>48.66999816894531</v>
@@ -5679,7 +5679,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.59231948852539</v>
+        <v>38.59232711791992</v>
       </c>
       <c r="C199" t="n">
         <v>41.66999816894531</v>
@@ -5708,7 +5708,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>45.03826522827148</v>
+        <v>45.03826904296875</v>
       </c>
       <c r="C200" t="n">
         <v>48.63000106811523</v>
@@ -5737,7 +5737,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>41.07392120361328</v>
+        <v>41.07391738891602</v>
       </c>
       <c r="C201" t="n">
         <v>44.13000106811523</v>
@@ -5766,7 +5766,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.2608528137207</v>
+        <v>34.26084899902344</v>
       </c>
       <c r="C202" t="n">
         <v>36.81000137329102</v>
@@ -5795,7 +5795,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>37.08100891113281</v>
+        <v>37.08101272583008</v>
       </c>
       <c r="C203" t="n">
         <v>39.84000015258789</v>
@@ -5824,7 +5824,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>42.50685501098633</v>
+        <v>42.50685119628906</v>
       </c>
       <c r="C204" t="n">
         <v>45.43999862670898</v>
@@ -5851,7 +5851,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>38.79311752319336</v>
+        <v>38.79311370849609</v>
       </c>
       <c r="C205" t="n">
         <v>41.47000122070312</v>
@@ -5878,7 +5878,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>46.30478286743164</v>
+        <v>46.30478668212891</v>
       </c>
       <c r="C206" t="n">
         <v>49.5</v>
@@ -5905,7 +5905,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>42.93715286254883</v>
+        <v>42.93716430664062</v>
       </c>
       <c r="C207" t="n">
         <v>45.90000152587891</v>
@@ -5932,7 +5932,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>41.74169921875</v>
+        <v>41.74169158935547</v>
       </c>
       <c r="C208" t="n">
         <v>44.36999893188477</v>
@@ -5959,7 +5959,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>43.67966842651367</v>
+        <v>43.67966079711914</v>
       </c>
       <c r="C209" t="n">
         <v>46.43000030517578</v>
@@ -6075,7 +6075,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>42.60828018188477</v>
+        <v>42.6082763671875</v>
       </c>
       <c r="C213" t="n">
         <v>44.77999877929688</v>
@@ -6133,7 +6133,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>37.32743835449219</v>
+        <v>37.32744216918945</v>
       </c>
       <c r="C215" t="n">
         <v>39.22999954223633</v>
@@ -6191,7 +6191,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>41.76143646240234</v>
+        <v>41.76142883300781</v>
       </c>
       <c r="C217" t="n">
         <v>43.61999893188477</v>
@@ -6336,7 +6336,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>52.45273208618164</v>
+        <v>52.45273590087891</v>
       </c>
       <c r="C222" t="n">
         <v>54.22000122070312</v>
@@ -6423,7 +6423,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>57.43831634521484</v>
+        <v>57.43831253051758</v>
       </c>
       <c r="C225" t="n">
         <v>59.09999847412109</v>
@@ -6568,7 +6568,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>65.85920715332031</v>
+        <v>65.85921478271484</v>
       </c>
       <c r="C230" t="n">
         <v>67.48000335693359</v>
@@ -6597,7 +6597,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>63.18501281738281</v>
+        <v>63.18502044677734</v>
       </c>
       <c r="C231" t="n">
         <v>64.73999786376953</v>
@@ -6626,7 +6626,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>66.40291595458984</v>
+        <v>66.40292358398438</v>
       </c>
       <c r="C232" t="n">
         <v>67.73000335693359</v>
@@ -6713,7 +6713,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>73.29325866699219</v>
+        <v>73.29326629638672</v>
       </c>
       <c r="C235" t="n">
         <v>74.45999908447266</v>
@@ -6800,7 +6800,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>89.80550384521484</v>
+        <v>89.80551147460938</v>
       </c>
       <c r="C238" t="n">
         <v>90.94999694824219</v>
@@ -6829,7 +6829,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>80.28681182861328</v>
+        <v>80.28681945800781</v>
       </c>
       <c r="C239" t="n">
         <v>81.30999755859375</v>
@@ -6916,7 +6916,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>90.38990020751953</v>
+        <v>90.389892578125</v>
       </c>
       <c r="C242" t="n">
         <v>91.22000122070312</v>
@@ -6945,7 +6945,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>90.03316497802734</v>
+        <v>90.03317260742188</v>
       </c>
       <c r="C243" t="n">
         <v>90.86000061035156</v>
